--- a/05_Mobilitet og infrastruktur/Persontransport og reisevaner/Mobilitetsdashboard/Brukes2024/Veiledningstekst.xlsx
+++ b/05_Mobilitet og infrastruktur/Persontransport og reisevaner/Mobilitetsdashboard/Brukes2024/Veiledningstekst.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29127"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://vestfoldfylke-my.sharepoint.com/personal/rasmus_palmqvist_vestfoldfylke_no/Documents/Dokumenter/GitHub/Ny mappe/Vestfold/05_Mobilitet og infrastruktur/Persontransport og reisevaner/Mobilitetsdashboard/Brukes2024/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="74" documentId="8_{DDFB194D-53E3-4BC3-BC68-30E66A797E45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{9678F9C2-EF45-4D93-90AE-8AFBFA426959}"/>
+  <xr:revisionPtr revIDLastSave="75" documentId="8_{DDFB194D-53E3-4BC3-BC68-30E66A797E45}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C534B848-AE61-44E4-A249-5408E8945DEE}"/>
   <bookViews>
-    <workbookView xWindow="1560" yWindow="1560" windowWidth="21600" windowHeight="11295" xr2:uid="{82DE7516-CBDE-45FF-9F1E-52480DA26130}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{82DE7516-CBDE-45FF-9F1E-52480DA26130}"/>
   </bookViews>
   <sheets>
     <sheet name="Ark1" sheetId="1" r:id="rId1"/>
@@ -101,10 +101,10 @@
     <t>Elsparkesykkel/elsykkel</t>
   </si>
   <si>
-    <t xml:space="preserve">Dette datasettet viser bruk av delte biler, fra de tre mobilitetspunktene som finnes sentralt i Tønsberg. Tjenesten ble etablert i september 2023 i mobilitetspunktet på Jernbanestasjonen. De to andre mobilitetspunktene ble etablert i mars 2024. </t>
-  </si>
-  <si>
     <t xml:space="preserve">Datasettet viser bruk av delt mikromobilitet i Sandefjord og Tønsberg. Tjenesten ble etablert i Sandefjord i januar 2025 og i mai 2025 i Tønsberg. Datene er levert av Ryde i begge byene. I Tønsberg tilbys både elsparkesykkel og elsykkel, i Sandefjord tilbys elsparkesykkel. Merk at man på menysiden med elsparkesykkel/elsykkel kan klikke seg videre til en kartløsning som viser hvor turerne starter og stopper. </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Dette datasettet viser bruk av delte biler, fra de tre mobilitetspunktene som finnes sentralt i Tønsberg, og de to som finnes i Sandefjord. Tjenesten ble etablert i september 2023 i mobilitetspunktet på Jernbanestasjonen i Tønsberg. De to andre mobilitetspunktene ble etablert i mars 2024 i Tønsberg. Mobilitetspunktene i Sandefjord ble etablert i oktober 2024. </t>
   </si>
 </sst>
 </file>
@@ -555,7 +555,7 @@
         <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="60" x14ac:dyDescent="0.25">
@@ -563,7 +563,7 @@
         <v>17</v>
       </c>
       <c r="B10" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
   </sheetData>
